--- a/data/staged/FGI_liveState.xlsx
+++ b/data/staged/FGI_liveState.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ap_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="location_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="labor_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ap_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="location_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labor_data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -574,11 +574,9 @@
       <c r="D2" t="n">
         <v>60</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0.62</v>
@@ -607,39 +605,19 @@
       <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -655,11 +633,9 @@
       <c r="D3" t="n">
         <v>60</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0.82</v>
@@ -688,32 +664,14 @@
       <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>0</v>
       </c>
@@ -732,11 +690,9 @@
       <c r="D4" t="n">
         <v>42</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0.74</v>
@@ -765,32 +721,14 @@
       <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>0</v>
       </c>
@@ -809,11 +747,9 @@
       <c r="D5" t="n">
         <v>76</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -842,32 +778,14 @@
       <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -886,11 +804,9 @@
       <c r="D6" t="n">
         <v>61</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0.64</v>
@@ -919,39 +835,19 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -967,11 +863,9 @@
       <c r="D7" t="n">
         <v>39</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1000,32 +894,14 @@
       <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>0</v>
       </c>
@@ -1044,11 +920,9 @@
       <c r="D8" t="n">
         <v>55</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0.62</v>
@@ -1077,32 +951,14 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>0</v>
       </c>
@@ -1121,11 +977,9 @@
       <c r="D9" t="n">
         <v>57</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0.98</v>
@@ -1154,32 +1008,14 @@
       <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>0</v>
       </c>
@@ -1198,11 +1034,9 @@
       <c r="D10" t="n">
         <v>52</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0.89</v>
@@ -1231,32 +1065,14 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -1275,11 +1091,9 @@
       <c r="D11" t="n">
         <v>44</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0.72</v>
@@ -1308,39 +1122,19 @@
       <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1356,11 +1150,9 @@
       <c r="D12" t="n">
         <v>36</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0.62</v>
@@ -1389,39 +1181,19 @@
       <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>3</v>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1437,11 +1209,9 @@
       <c r="D13" t="n">
         <v>51</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0.62</v>
@@ -1470,39 +1240,19 @@
       <c r="O13" t="n">
         <v>3</v>
       </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>0</v>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y13" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1518,11 +1268,9 @@
       <c r="D14" t="n">
         <v>27</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0.92</v>
@@ -1551,39 +1299,19 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>5</v>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1599,11 +1327,9 @@
       <c r="D15" t="n">
         <v>47</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0.67</v>
@@ -1632,39 +1358,19 @@
       <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>4</v>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1680,11 +1386,9 @@
       <c r="D16" t="n">
         <v>56</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0.68</v>
@@ -1713,39 +1417,19 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>4</v>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1761,11 +1445,9 @@
       <c r="D17" t="n">
         <v>45</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0.7</v>
@@ -1794,39 +1476,19 @@
       <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>7</v>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y17" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1842,11 +1504,9 @@
       <c r="D18" t="n">
         <v>63</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0.5</v>
@@ -1875,39 +1535,19 @@
       <c r="O18" t="n">
         <v>6</v>
       </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1923,11 +1563,9 @@
       <c r="D19" t="n">
         <v>42</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0.59</v>
@@ -1956,39 +1594,19 @@
       <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2004,11 +1622,9 @@
       <c r="D20" t="n">
         <v>67</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0.54</v>
@@ -2037,39 +1653,19 @@
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>4</v>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2085,11 +1681,9 @@
       <c r="D21" t="n">
         <v>66</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0.72</v>
@@ -2118,39 +1712,19 @@
       <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>2</v>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y21" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -2166,11 +1740,9 @@
       <c r="D22" t="n">
         <v>93</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0.64</v>
@@ -2199,39 +1771,19 @@
       <c r="O22" t="n">
         <v>7</v>
       </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y22" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2247,11 +1799,9 @@
       <c r="D23" t="n">
         <v>36</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0.84</v>
@@ -2280,39 +1830,19 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>1</v>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y23" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2328,11 +1858,9 @@
       <c r="D24" t="n">
         <v>54</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0.77</v>
@@ -2361,39 +1889,19 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y24" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -2409,11 +1917,9 @@
       <c r="D25" t="n">
         <v>50</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
@@ -2442,39 +1948,19 @@
       <c r="O25" t="n">
         <v>4</v>
       </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -2490,11 +1976,9 @@
       <c r="D26" t="n">
         <v>47</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0.82</v>
@@ -2523,39 +2007,19 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2571,11 +2035,9 @@
       <c r="D27" t="n">
         <v>42</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0.92</v>
@@ -2604,39 +2066,19 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -2652,11 +2094,9 @@
       <c r="D28" t="n">
         <v>51</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.68</v>
@@ -2685,39 +2125,19 @@
       <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>2</v>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y28" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2733,11 +2153,9 @@
       <c r="D29" t="n">
         <v>45</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0.7</v>
@@ -2766,39 +2184,19 @@
       <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>0</v>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y29" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -2814,11 +2212,9 @@
       <c r="D30" t="n">
         <v>42</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0.89</v>
@@ -2847,39 +2243,19 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -2895,11 +2271,9 @@
       <c r="D31" t="n">
         <v>35</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.86</v>
@@ -2928,39 +2302,19 @@
       <c r="O31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y31" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -2976,11 +2330,9 @@
       <c r="D32" t="n">
         <v>26</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.87</v>
@@ -3009,39 +2361,19 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y32" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3057,11 +2389,9 @@
       <c r="D33" t="n">
         <v>40</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.77</v>
@@ -3090,39 +2420,19 @@
       <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3138,11 +2448,9 @@
       <c r="D34" t="n">
         <v>38</v>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0.68</v>
@@ -3171,39 +2479,19 @@
       <c r="O34" t="n">
         <v>4</v>
       </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="35">
@@ -3219,11 +2507,9 @@
       <c r="D35" t="n">
         <v>33</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.64</v>
@@ -3252,39 +2538,19 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>1</v>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y35" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3300,11 +2566,9 @@
       <c r="D36" t="n">
         <v>28</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0.67</v>
@@ -3333,39 +2597,19 @@
       <c r="O36" t="n">
         <v>4</v>
       </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>1</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>1</v>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3381,11 +2625,9 @@
       <c r="D37" t="n">
         <v>35</v>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0.68</v>
@@ -3414,39 +2656,19 @@
       <c r="O37" t="n">
         <v>2</v>
       </c>
-      <c r="P37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>1</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>1</v>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y37" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -3462,11 +2684,9 @@
       <c r="D38" t="n">
         <v>40</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0.72</v>
@@ -3495,39 +2715,19 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="P38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>3</v>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3543,11 +2743,9 @@
       <c r="D39" t="n">
         <v>19</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0.8</v>
@@ -3576,39 +2774,19 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>5</v>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y39" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -3624,11 +2802,9 @@
       <c r="D40" t="n">
         <v>32</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0.8</v>
@@ -3657,39 +2833,19 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>0</v>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y40" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -3705,11 +2861,9 @@
       <c r="D41" t="n">
         <v>46</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0.83</v>
@@ -3738,39 +2892,19 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>6</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>0</v>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y41" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -3786,11 +2920,9 @@
       <c r="D42" t="n">
         <v>60</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0.68</v>
@@ -3819,39 +2951,19 @@
       <c r="O42" t="n">
         <v>5</v>
       </c>
-      <c r="P42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>0</v>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y42" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3867,11 +2979,9 @@
       <c r="D43" t="n">
         <v>61</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0.57</v>
@@ -3900,39 +3010,19 @@
       <c r="O43" t="n">
         <v>6</v>
       </c>
-      <c r="P43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>6</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>0</v>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y43" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -3948,11 +3038,9 @@
       <c r="D44" t="n">
         <v>47</v>
       </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0.51</v>
@@ -3981,39 +3069,19 @@
       <c r="O44" t="n">
         <v>7</v>
       </c>
-      <c r="P44" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>6</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>2</v>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y44" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -4029,11 +3097,9 @@
       <c r="D45" t="n">
         <v>51</v>
       </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0.64</v>
@@ -4062,39 +3128,19 @@
       <c r="O45" t="n">
         <v>6</v>
       </c>
-      <c r="P45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>0</v>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y45" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -4110,11 +3156,9 @@
       <c r="D46" t="n">
         <v>46</v>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0.71</v>
@@ -4143,39 +3187,19 @@
       <c r="O46" t="n">
         <v>5</v>
       </c>
-      <c r="P46" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>6</v>
-      </c>
-      <c r="R46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>0</v>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y46" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4191,11 +3215,9 @@
       <c r="D47" t="n">
         <v>37</v>
       </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0.7</v>
@@ -4224,39 +3246,19 @@
       <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="P47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>6</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>2</v>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y47" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -4272,11 +3274,9 @@
       <c r="D48" t="n">
         <v>59</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0.67</v>
@@ -4305,32 +3305,14 @@
       <c r="O48" t="n">
         <v>5</v>
       </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>0</v>
       </c>
@@ -4349,11 +3331,9 @@
       <c r="D49" t="n">
         <v>42</v>
       </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0.71</v>
@@ -4382,39 +3362,19 @@
       <c r="O49" t="n">
         <v>4</v>
       </c>
-      <c r="P49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" t="n">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>6</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -4430,11 +3390,9 @@
       <c r="D50" t="n">
         <v>74</v>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0.62</v>
@@ -4463,39 +3421,19 @@
       <c r="O50" t="n">
         <v>6</v>
       </c>
-      <c r="P50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>6</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W50" t="n">
-        <v>1</v>
-      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>3</v>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y50" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4511,11 +3449,9 @@
       <c r="D51" t="n">
         <v>56</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0.66</v>
@@ -4544,39 +3480,19 @@
       <c r="O51" t="n">
         <v>5</v>
       </c>
-      <c r="P51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y51" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -4592,11 +3508,9 @@
       <c r="D52" t="n">
         <v>77</v>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0.71</v>
@@ -4625,39 +3539,19 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="P52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>6</v>
-      </c>
-      <c r="R52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>2</v>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y52" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -4673,11 +3567,9 @@
       <c r="D53" t="n">
         <v>67</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0.6899999999999999</v>
@@ -4706,32 +3598,14 @@
       <c r="O53" t="n">
         <v>7</v>
       </c>
-      <c r="P53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2</v>
-      </c>
-      <c r="T53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W53" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>0</v>
       </c>
@@ -4750,11 +3624,9 @@
       <c r="D54" t="n">
         <v>80</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0.47</v>
@@ -4783,39 +3655,19 @@
       <c r="O54" t="n">
         <v>8</v>
       </c>
-      <c r="P54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>6</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>2</v>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y54" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -4831,11 +3683,9 @@
       <c r="D55" t="n">
         <v>67</v>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.68</v>
@@ -4864,39 +3714,19 @@
       <c r="O55" t="n">
         <v>5</v>
       </c>
-      <c r="P55" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>6</v>
-      </c>
-      <c r="R55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>1</v>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y55" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -4912,11 +3742,9 @@
       <c r="D56" t="n">
         <v>58</v>
       </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.59</v>
@@ -4945,39 +3773,19 @@
       <c r="O56" t="n">
         <v>6</v>
       </c>
-      <c r="P56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>6</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W56" t="n">
-        <v>1</v>
-      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>3</v>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y56" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -4993,11 +3801,9 @@
       <c r="D57" t="n">
         <v>59</v>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0.8100000000000001</v>
@@ -5026,39 +3832,19 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="P57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W57" t="n">
-        <v>1</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>3</v>
       </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y57" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -5074,11 +3860,9 @@
       <c r="D58" t="n">
         <v>60</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0.76</v>
@@ -5107,39 +3891,19 @@
       <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="P58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W58" t="n">
-        <v>1</v>
-      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>2</v>
       </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y58" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -5155,11 +3919,9 @@
       <c r="D59" t="n">
         <v>38</v>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0.9</v>
@@ -5188,39 +3950,19 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>6</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W59" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>1</v>
       </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y59" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -5236,11 +3978,9 @@
       <c r="D60" t="n">
         <v>71</v>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>0.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0.88</v>
@@ -5269,39 +4009,19 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="P60" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>6</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W60" t="n">
-        <v>1</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>0</v>
       </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y60" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -5317,11 +4037,9 @@
       <c r="D61" t="n">
         <v>54</v>
       </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>0.72</v>
@@ -5350,39 +4068,19 @@
       <c r="O61" t="n">
         <v>4</v>
       </c>
-      <c r="P61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>6</v>
-      </c>
-      <c r="R61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W61" t="n">
-        <v>1</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>0</v>
       </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y61" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -5398,11 +4096,9 @@
       <c r="D62" t="n">
         <v>101</v>
       </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0.5600000000000001</v>
@@ -5431,39 +4127,19 @@
       <c r="O62" t="n">
         <v>5</v>
       </c>
-      <c r="P62" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>6</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W62" t="n">
-        <v>1</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
         <v>4</v>
       </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y62" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -5479,11 +4155,9 @@
       <c r="D63" t="n">
         <v>67</v>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>0.727272727272727</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0.5600000000000001</v>
@@ -5512,39 +4186,19 @@
       <c r="O63" t="n">
         <v>6</v>
       </c>
-      <c r="P63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>6</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W63" t="n">
-        <v>1</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
         <v>0</v>
       </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y63" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -5560,11 +4214,9 @@
       <c r="D64" t="n">
         <v>85</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>0.545454545454545</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0.52</v>
@@ -5593,39 +4245,19 @@
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="P64" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W64" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>0</v>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y64" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -5641,11 +4273,9 @@
       <c r="D65" t="n">
         <v>27</v>
       </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0.85</v>
@@ -5674,39 +4304,19 @@
       <c r="O65" t="n">
         <v>2</v>
       </c>
-      <c r="P65" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>6</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1</v>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W65" t="n">
-        <v>1</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>5</v>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y65" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -5722,11 +4332,9 @@
       <c r="D66" t="n">
         <v>39</v>
       </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0.73</v>
@@ -5755,39 +4363,19 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
-      <c r="P66" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q66" t="n">
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>6</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2</v>
-      </c>
-      <c r="T66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W66" t="n">
-        <v>1</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -5803,11 +4391,9 @@
       <c r="D67" t="n">
         <v>63</v>
       </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0.5600000000000001</v>
@@ -5836,39 +4422,19 @@
       <c r="O67" t="n">
         <v>5</v>
       </c>
-      <c r="P67" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>6</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W67" t="n">
-        <v>1</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>0</v>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y67" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -5884,11 +4450,9 @@
       <c r="D68" t="n">
         <v>44</v>
       </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>0.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0.66</v>
@@ -5917,39 +4481,19 @@
       <c r="O68" t="n">
         <v>4</v>
       </c>
-      <c r="P68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>6</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2</v>
-      </c>
-      <c r="T68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W68" t="n">
-        <v>1</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>0</v>
       </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y68" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -5965,11 +4509,9 @@
       <c r="D69" t="n">
         <v>49</v>
       </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0.7</v>
@@ -5998,39 +4540,19 @@
       <c r="O69" t="n">
         <v>3</v>
       </c>
-      <c r="P69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>6</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1</v>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W69" t="n">
-        <v>1</v>
-      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
         <v>3</v>
       </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y69" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -6046,11 +4568,9 @@
       <c r="D70" t="n">
         <v>37</v>
       </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0.77</v>
@@ -6079,39 +4599,19 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="P70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q70" t="n">
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
         <v>6</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2</v>
-      </c>
-      <c r="T70" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -6127,11 +4627,9 @@
       <c r="D71" t="n">
         <v>50</v>
       </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0.72</v>
@@ -6160,39 +4658,19 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="P71" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>6</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W71" t="n">
-        <v>1</v>
-      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>1</v>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y71" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -6208,11 +4686,9 @@
       <c r="D72" t="n">
         <v>68</v>
       </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0.63</v>
@@ -6241,39 +4717,19 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>6</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W72" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>0</v>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y72" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -6289,11 +4745,9 @@
       <c r="D73" t="n">
         <v>32</v>
       </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0.8</v>
@@ -6322,39 +4776,19 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="P73" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>6</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2</v>
-      </c>
-      <c r="T73" t="n">
-        <v>1</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W73" t="n">
-        <v>1</v>
-      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>7</v>
       </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y73" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -6370,11 +4804,9 @@
       <c r="D74" t="n">
         <v>37</v>
       </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0.74</v>
@@ -6403,39 +4835,19 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="P74" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1</v>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W74" t="n">
-        <v>1</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>0</v>
       </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -6451,11 +4863,9 @@
       <c r="D75" t="n">
         <v>29</v>
       </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0.8</v>
@@ -6484,39 +4894,19 @@
       <c r="O75" t="n">
         <v>2</v>
       </c>
-      <c r="P75" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>6</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
-        <v>2</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1</v>
-      </c>
-      <c r="U75" t="n">
-        <v>1</v>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W75" t="n">
-        <v>1</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>6</v>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y75" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -6532,11 +4922,9 @@
       <c r="D76" t="n">
         <v>48</v>
       </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0.62</v>
@@ -6565,39 +4953,19 @@
       <c r="O76" t="n">
         <v>3</v>
       </c>
-      <c r="P76" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>6</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W76" t="n">
-        <v>1</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>4</v>
       </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y76" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -6613,11 +4981,9 @@
       <c r="D77" t="n">
         <v>35</v>
       </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0.7</v>
@@ -6646,39 +5012,19 @@
       <c r="O77" t="n">
         <v>2</v>
       </c>
-      <c r="P77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>6</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="n">
-        <v>2</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="W77" t="n">
-        <v>1</v>
-      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
       <c r="X77" t="n">
         <v>7</v>
       </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y77" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -6694,11 +5040,9 @@
       <c r="D78" t="n">
         <v>45</v>
       </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0.8</v>
@@ -6727,39 +5071,19 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="P78" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>6</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>2</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W78" t="n">
-        <v>1</v>
-      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>4</v>
       </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y78" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -6775,11 +5099,9 @@
       <c r="D79" t="n">
         <v>47</v>
       </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0.72</v>
@@ -6808,39 +5130,19 @@
       <c r="O79" t="n">
         <v>4</v>
       </c>
-      <c r="P79" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
-        <v>1</v>
-      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
       <c r="X79" t="n">
         <v>7</v>
       </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y79" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6856,11 +5158,9 @@
       <c r="D80" t="n">
         <v>35</v>
       </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>0.954545454545455</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0.78</v>
@@ -6889,39 +5189,19 @@
       <c r="O80" t="n">
         <v>3</v>
       </c>
-      <c r="P80" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q80" t="n">
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
         <v>6</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>2</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1</v>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
-        <v>1</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="81">
@@ -6937,11 +5217,9 @@
       <c r="D81" t="n">
         <v>55</v>
       </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0.6899999999999999</v>
@@ -6970,39 +5248,19 @@
       <c r="O81" t="n">
         <v>3</v>
       </c>
-      <c r="P81" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>6</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>2</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W81" t="n">
-        <v>1</v>
-      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>6</v>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y81" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -7018,11 +5276,9 @@
       <c r="D82" t="n">
         <v>63</v>
       </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>0.772727272727273</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0.78</v>
@@ -7051,39 +5307,19 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="P82" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>6</v>
-      </c>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
-      <c r="S82" t="n">
-        <v>2</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W82" t="n">
-        <v>1</v>
-      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
       <c r="X82" t="n">
         <v>5</v>
       </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y82" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -7099,11 +5335,9 @@
       <c r="D83" t="n">
         <v>56</v>
       </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.863636363636364</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0.71</v>
@@ -7132,39 +5366,19 @@
       <c r="O83" t="n">
         <v>4</v>
       </c>
-      <c r="P83" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>6</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1</v>
-      </c>
-      <c r="S83" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W83" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>7</v>
       </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y83" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -7180,11 +5394,9 @@
       <c r="D84" t="n">
         <v>62</v>
       </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.9090909090909089</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>0.73</v>
@@ -7213,39 +5425,19 @@
       <c r="O84" t="n">
         <v>4</v>
       </c>
-      <c r="P84" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>6</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
-      <c r="S84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1</v>
-      </c>
-      <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W84" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
       <c r="X84" t="n">
         <v>4</v>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y84" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -7261,11 +5453,9 @@
       <c r="D85" t="n">
         <v>54</v>
       </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>0.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0.58</v>
@@ -7294,39 +5484,19 @@
       <c r="O85" t="n">
         <v>5</v>
       </c>
-      <c r="P85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>6</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
-      <c r="S85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
-        <v>1</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W85" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
       <c r="X85" t="n">
         <v>4</v>
       </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y85" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -7342,11 +5512,9 @@
       <c r="D86" t="n">
         <v>61</v>
       </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>0.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0.88</v>
@@ -7375,39 +5543,19 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="P86" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>6</v>
-      </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="S86" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W86" t="n">
-        <v>1</v>
-      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>5</v>
       </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y86" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -7423,11 +5571,9 @@
       <c r="D87" t="n">
         <v>79</v>
       </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>0.636363636363636</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0.67</v>
@@ -7456,39 +5602,19 @@
       <c r="O87" t="n">
         <v>6</v>
       </c>
-      <c r="P87" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>6</v>
-      </c>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
-      <c r="S87" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1</v>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W87" t="n">
-        <v>1</v>
-      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
       <c r="X87" t="n">
         <v>4</v>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y87" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -7504,11 +5630,9 @@
       <c r="D88" t="n">
         <v>61</v>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>0.5909090909090911</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0.61</v>
@@ -7537,39 +5661,19 @@
       <c r="O88" t="n">
         <v>6</v>
       </c>
-      <c r="P88" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>6</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
-        <v>2</v>
-      </c>
-      <c r="T88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>1</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>2</v>
       </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y88" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -7585,11 +5689,9 @@
       <c r="D89" t="n">
         <v>64</v>
       </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.5909090909090911</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0.75</v>
@@ -7618,39 +5720,19 @@
       <c r="O89" t="n">
         <v>4</v>
       </c>
-      <c r="P89" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>6</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>2</v>
-      </c>
-      <c r="T89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W89" t="n">
-        <v>1</v>
-      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
       <c r="X89" t="n">
         <v>5</v>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y89" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -7666,11 +5748,9 @@
       <c r="D90" t="n">
         <v>106</v>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.454545454545455</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -7699,39 +5779,19 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="P90" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>6</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="n">
-        <v>2</v>
-      </c>
-      <c r="T90" t="n">
-        <v>1</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
         <v>4</v>
       </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y90" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -7747,11 +5807,9 @@
       <c r="D91" t="n">
         <v>66</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>0.454545454545455</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0.96</v>
@@ -7780,39 +5838,19 @@
       <c r="O91" t="n">
         <v>4</v>
       </c>
-      <c r="P91" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>6</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>2</v>
-      </c>
-      <c r="T91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
       <c r="X91" t="n">
         <v>3</v>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y91" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -7828,11 +5866,9 @@
       <c r="D92" t="n">
         <v>71</v>
       </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>0.636363636363636</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0.73</v>
@@ -7861,39 +5897,19 @@
       <c r="O92" t="n">
         <v>5</v>
       </c>
-      <c r="P92" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q92" t="n">
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y92" t="n">
         <v>6</v>
-      </c>
-      <c r="R92" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" t="n">
-        <v>2</v>
-      </c>
-      <c r="T92" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" t="n">
-        <v>1</v>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W92" t="n">
-        <v>1</v>
-      </c>
-      <c r="X92" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -7909,11 +5925,9 @@
       <c r="D93" t="n">
         <v>69</v>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>0.5909090909090911</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0.73</v>
@@ -7942,39 +5956,19 @@
       <c r="O93" t="n">
         <v>5</v>
       </c>
-      <c r="P93" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>4</v>
-      </c>
-      <c r="R93" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S93" t="n">
-        <v>2</v>
-      </c>
-      <c r="T93" t="n">
-        <v>1</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1</v>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>GE</t>
-        </is>
-      </c>
-      <c r="W93" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>4</v>
       </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y93" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -7992,7 +5986,7 @@
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>0.454545454545455</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0.76</v>
@@ -8032,10 +6026,8 @@
       <c r="X94" t="n">
         <v>5</v>
       </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y94" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8049,7 +6041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8111,7 +6103,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8143,7 +6135,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -9031,108 +7023,6 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>**Disclaimer -  this data does not reflect actual Boeing Production System Data or PI</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BSC1</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>8</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Paint</t>
-        </is>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>C1, C2, C3, C3.5, C4</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Added for scheduler paint move logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BSC2</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Paint</t>
-        </is>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>C1, C2, C3, C3.5, C4, C5</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Added for scheduler paint move logic</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9145,7 +7035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9431,7 +7321,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -9448,42 +7338,6 @@
       </c>
       <c r="D17" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>STARTDATE</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ENDDATE</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
       </c>
     </row>
   </sheetData>
